--- a/tests/fixtures/banco_fixture_classe.xlsx
+++ b/tests/fixtures/banco_fixture_classe.xlsx
@@ -1,44 +1,40 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="28680" yWindow="-120" windowWidth="38640" windowHeight="15720" tabRatio="600" firstSheet="3" activeTab="10" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="unidade-regional" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="regional-superintendencia" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="superintendencia-cidade" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="cidade-sistema" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="sistema-topologia" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="cidade-operacional" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="subbacia-operacional" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="componentes-subbacias-capex" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ete-capex" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="regional-operacional" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="metas-cobertura" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="fator-esgoto" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="unidade-regional" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="regional-superintendencia" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="superintendencia-cidade" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="cidade-sistema" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="sistema-topologia" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="cidade-operacional" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="subbacia-operacional" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="componentes-subbacias-capex" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="ete-capex" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="regional-operacional" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="metas-cobertura" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="fator-esgoto" sheetId="12" state="visible" r:id="rId12"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="0" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <b val="1"/>
-      <sz val="11"/>
     </font>
   </fonts>
   <fills count="2">
@@ -61,12 +57,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -430,30 +425,30 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:E2"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>regional_id</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>regional_name</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>unidade_id</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>unidade_name</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>wacc_medio</t>
         </is>
@@ -496,15 +491,15 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:B2"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>regional_id</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>ano_base</t>
         </is>
@@ -532,20 +527,20 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:C5"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>cidade_id</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>ano</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>cobertura_pct</t>
         </is>
@@ -615,25 +610,25 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:D7"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>cidade_id</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>cidade_name</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>cobertura_pct</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>paridade</t>
         </is>
@@ -759,20 +754,20 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:C2"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>unidade_id</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>superintendencia_id</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>superintendencia_name</t>
         </is>
@@ -807,20 +802,20 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:C3"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>superintendencia_id</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>cidade_id</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>cidade_name</t>
         </is>
@@ -872,20 +867,20 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:C3"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>cidade_id</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>sistema_id</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>sistema_name</t>
         </is>
@@ -937,25 +932,25 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:D5"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>sistema_id</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>componente_sistema_id</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>componente_sistema_nome</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>componente_sistema_id_jusante</t>
         </is>
@@ -1061,20 +1056,20 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:C3"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>cidade_id</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>data_fim_concessao</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>unidade_cobertura</t>
         </is>
@@ -1121,118 +1116,113 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V5"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
+  <dimension ref="A1:U5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>sub_bacia</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>preco_por_ligacao</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>receita_faturada_media_mensal</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>receita_arrecadada_media_mensal</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>tempo_arrecadacao</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>tempo_ramp_up</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>vazao_contribuicao</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>universo_ligacoes</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>ligacoes_atuais</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>ligacoes_novas_obras</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>universo_economias</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>economias_atuais</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>economias_novas_obras</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>universo_populacao</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>populacao_atual</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>populacao_novas_obras</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>potencial_crescimento</t>
         </is>
       </c>
       <c r="R1" t="inlineStr">
         <is>
-          <t>universo_ligacoes_industrial</t>
+          <t>universo_ligacoes_residencial</t>
         </is>
       </c>
       <c r="S1" t="inlineStr">
         <is>
-          <t>ligacoes_atuais_industrial</t>
+          <t>ligacoes_atuais_residencial</t>
         </is>
       </c>
       <c r="T1" t="inlineStr">
         <is>
-          <t>receita_faturada_industrial</t>
+          <t>universo_economias_residencial</t>
         </is>
       </c>
       <c r="U1" t="inlineStr">
         <is>
-          <t>receita_arrecadada_industrial</t>
-        </is>
-      </c>
-      <c r="V1" t="inlineStr">
-        <is>
-          <t>vazao_contribuicao_industrial</t>
+          <t>economias_atuais_residencial</t>
         </is>
       </c>
     </row>
@@ -1291,19 +1281,16 @@
         <v>1</v>
       </c>
       <c r="R2" t="n">
-        <v>200</v>
+        <v>800</v>
       </c>
       <c r="S2" t="n">
-        <v>80</v>
+        <v>320</v>
       </c>
       <c r="T2" t="n">
-        <v>18000</v>
+        <v>880</v>
       </c>
       <c r="U2" t="n">
-        <v>15000</v>
-      </c>
-      <c r="V2" t="n">
-        <v>20</v>
+        <v>352</v>
       </c>
     </row>
     <row r="3">
@@ -1360,6 +1347,18 @@
       <c r="Q3" t="n">
         <v>1</v>
       </c>
+      <c r="R3" t="n">
+        <v>900</v>
+      </c>
+      <c r="S3" t="n">
+        <v>300</v>
+      </c>
+      <c r="T3" t="n">
+        <v>990</v>
+      </c>
+      <c r="U3" t="n">
+        <v>330</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1416,19 +1415,16 @@
         <v>1</v>
       </c>
       <c r="R4" t="n">
-        <v>160</v>
+        <v>640</v>
       </c>
       <c r="S4" t="n">
-        <v>70</v>
+        <v>280</v>
       </c>
       <c r="T4" t="n">
-        <v>14000</v>
+        <v>704</v>
       </c>
       <c r="U4" t="n">
-        <v>11000</v>
-      </c>
-      <c r="V4" t="n">
-        <v>15</v>
+        <v>308</v>
       </c>
     </row>
     <row r="5">
@@ -1484,6 +1480,18 @@
       </c>
       <c r="Q5" t="n">
         <v>1</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1200</v>
+      </c>
+      <c r="S5" t="n">
+        <v>500</v>
+      </c>
+      <c r="T5" t="n">
+        <v>1320</v>
+      </c>
+      <c r="U5" t="n">
+        <v>550</v>
       </c>
     </row>
   </sheetData>
@@ -1498,65 +1506,65 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:L21"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>sub_bacia</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>componente</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>quantidade</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>unidade</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>preco_unitario</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>capex</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>opex</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>tempo_predecessoras</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>tempo_execucao</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>obra_obrigatoria_ano</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>obra_proibida_ate</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>wacc</t>
         </is>
@@ -2454,80 +2462,80 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:O3"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>ete_id</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>capacidade_por_modulo</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>capex_por_modulo</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>opex_por_modulo</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>tempo_predecessoras</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>tempo_de_execucao</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>capacidade_nominal_atual</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>vazao_de_operacao_atual</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>capacidade_ociosa</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>nova</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>capex_terreno</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>modulos</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>obra_obrigatoria_ano</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>obra_proibida_ate</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>wacc</t>
         </is>
